--- a/analysis_outputs/data/mental_rehearsal_ablation_results.xlsx
+++ b/analysis_outputs/data/mental_rehearsal_ablation_results.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="responses" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="questionnaire_responses" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="responses_v0" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="responses" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="questionnaire_responses" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4777" uniqueCount="1956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="2372">
   <si>
     <t>receivedAt</t>
   </si>
@@ -50,7 +51,7 @@
     <t>rightRating</t>
   </si>
   <si>
-    <t>reason</t>
+    <t>improvement</t>
   </si>
   <si>
     <t>startedAt</t>
@@ -4331,7 +4332,7 @@
     <t>2026-06-05T22:51:32.655Z</t>
   </si>
   <si>
-    <t>2026-06-05T22:51:35.909Z</t>
+    <t>2026-06-05T23:11:46.473Z</t>
   </si>
   <si>
     <t>67c045fa5074c5500ca40e76:42:0</t>
@@ -4343,7 +4344,7 @@
     <t>2026-06-05T22:46:17.479Z</t>
   </si>
   <si>
-    <t>2026-06-05T22:51:32.782Z</t>
+    <t>2026-06-05T23:11:44.008Z</t>
   </si>
   <si>
     <t>2026-06-05T22:52:17.590Z</t>
@@ -4583,7 +4584,7 @@
     <t>2026-06-05T22:56:45.657Z</t>
   </si>
   <si>
-    <t>2026-06-05T22:57:39.412Z</t>
+    <t>2026-06-05T23:11:52.616Z</t>
   </si>
   <si>
     <t>67c045fa5074c5500ca40e76:42:1</t>
@@ -4592,7 +4593,7 @@
     <t>2026-06-05T22:51:37.794Z</t>
   </si>
   <si>
-    <t>2026-06-05T22:57:36.330Z</t>
+    <t>2026-06-05T23:11:50.171Z</t>
   </si>
   <si>
     <t>2026-06-05T22:57:52.502Z</t>
@@ -4703,7 +4704,7 @@
     <t>2026-06-05T23:00:28.076Z</t>
   </si>
   <si>
-    <t>2026-06-05T23:00:42.866Z</t>
+    <t>2026-06-05T23:11:59.395Z</t>
   </si>
   <si>
     <t>67c045fa5074c5500ca40e76:42:2</t>
@@ -4712,7 +4713,7 @@
     <t>2026-06-05T22:57:41.622Z</t>
   </si>
   <si>
-    <t>2026-06-05T23:00:39.581Z</t>
+    <t>2026-06-05T23:11:56.778Z</t>
   </si>
   <si>
     <t>2026-06-05T23:01:03.249Z</t>
@@ -4739,6 +4740,948 @@
     <t>2026-06-05T23:01:11.730Z</t>
   </si>
   <si>
+    <t>2026-06-05T23:01:23.128Z</t>
+  </si>
+  <si>
+    <t>60843a5bac9fbcc4a389cf29:8:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:59:04.179Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:01:19.979Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:01:30.079Z</t>
+  </si>
+  <si>
+    <t>6a00297ff9c814c9d89abd9d:30:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:58:32.556Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:00:32.254Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:52.708Z</t>
+  </si>
+  <si>
+    <t>60843a5bac9fbcc4a389cf29:8:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:01:24.540Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:50.340Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:11.099Z</t>
+  </si>
+  <si>
+    <t>6a16e48625a8729b8578bbaa:12:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:56:53.335Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:11.255Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:04.682Z</t>
+  </si>
+  <si>
+    <t>67c045fa5074c5500ca40e76:42:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:00:44.827Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:02.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:04:21.174Z</t>
+  </si>
+  <si>
+    <t>6984afed1eac95dcf5fbe02d:25:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:01:15.617Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:04:19.545Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:04:25.543Z</t>
+  </si>
+  <si>
+    <t>6a00297ff9c814c9d89abd9d:30:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:00:34.738Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:27.489Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:05:10.965Z</t>
+  </si>
+  <si>
+    <t>6984afed1eac95dcf5fbe02d:25:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:04:22.434Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:05:09.017Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:06:55.047Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:0</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:27.105Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:06:54.164Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:09.863Z</t>
+  </si>
+  <si>
+    <t>67c045fa5074c5500ca40e76:42:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:33.850Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:07.860Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:09:57.861Z</t>
+  </si>
+  <si>
+    <t>6a16e48625a8729b8578bbaa:12:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:13.741Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:09:58.095Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:10:03.638Z</t>
+  </si>
+  <si>
+    <t>6a229a63b2044a3b6694cdf5:32:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:01:04.656Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:10:01.096Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:03.628Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:06:56.717Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:02.709Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:13:22.309Z</t>
+  </si>
+  <si>
+    <t>67c045fa5074c5500ca40e76:42:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:11.265Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:13:19.329Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:06.202Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:0</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:10:04.552Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:01.829Z</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/149.0.0.0 Safari/537.36 Edg/149.0.0.0</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:23.173Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:12:05.266Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:21.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:16:59.228Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:05.763Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:16:55.723Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:20.519Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:15:24.708Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:19.627Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:47.087Z</t>
+  </si>
+  <si>
+    <t>6a16e48625a8729b8578bbaa:12:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:10:01.626Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:47.392Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:20.821Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:16:58.726Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:17.055Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:56.387Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:0</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:57.705Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:54.173Z</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (iPhone; CPU iPhone OS 18_7 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Version/26.5 Mobile/15E148 Safari/604.1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:03.934Z</t>
+  </si>
+  <si>
+    <t>6a229a63b2044a3b6694cdf5:32:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:10:04.569Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:00.840Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:30.708Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:20.451Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:26.897Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:20:24.290Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:57.983Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:20:20.136Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:15.629Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:30.286Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:11.424Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:19.634Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:20:23.162Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:17.078Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:45.938Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:22.001Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:44.028Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:58.971Z</t>
+  </si>
+  <si>
+    <t>6a16e48625a8729b8578bbaa:12:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:17:49.774Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:59.208Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:21.842Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:20.871Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:20.106Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:33.211Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:15.742Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:29.311Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:31.696Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:23.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:29.836Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:53.972Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:21:47.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:53.230Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:24:20.217Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:33.022Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:24:18.818Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:27:14.645Z</t>
+  </si>
+  <si>
+    <t>6a229a63b2044a3b6694cdf5:32:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:05.133Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:27:12.814Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:35:41.620Z</t>
+  </si>
+  <si>
+    <t>6a229a63b2044a3b6694cdf5:32:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:27:15.666Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:35:39.246Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:40:09.811Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:0</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:35:34.472Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:40:09.585Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:41:01.477Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:0</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:35:23.965Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:40:56.696Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:43:11.460Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:40:13.559Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:43:10.479Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:44:40.872Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:41:03.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:44:35.796Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:45:22.112Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:43:15.067Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:45:22.363Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:46:22.785Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:45:25.744Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:46:22.920Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:09.396Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:44:40.654Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:04.541Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:47.594Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:46:26.999Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:46.782Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:48:32.028Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:09.798Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:48:26.803Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:48:58.947Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:0</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:46:58.102Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:48:58.160Z</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (Windows NT 10.0; Win64; x64; rv:150.0) Gecko/20100101 Firefox/150.0</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:49:25.068Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:47:52.035Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:49:24.990Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:50:31.154Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:49:01.773Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:50:30.602Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:20.400Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:50:34.084Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:20.357Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:38.429Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:48:32.366Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:34.832Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:53:51.100Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:3</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:22.857Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:53:50.962Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:54:11.531Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:39.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:54:07.160Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:20.131Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:4</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:53:53.621Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:20.001Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:56.934Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:0</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:53:06.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:55.104Z</t>
+  </si>
+  <si>
+    <t>Mozilla/5.0 (Macintosh; Intel Mac OS X 10_15_7) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/128.0.0.0 Safari/537.36</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:56:32.570Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:22.682Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:56:32.034Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:59:44.757Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:1</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:55:58.239Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:59:42.929Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:03:14.155Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:59:45.741Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:03:12.512Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:04:52.068Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:3</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:03:15.035Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:04:50.256Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:08:47.692Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:4</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:04:53.165Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:08:45.567Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:10:58.364Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:5</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:08:49.674Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:10:55.977Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:45:52.276Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:0</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:20:00.997Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:45:48.413Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:48:40.399Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:1</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:45:53.443Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:48:38.257Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:53:09.634Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:2</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:48:41.574Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:53:05.827Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:58:09.146Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:3</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:53:12.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:58:07.278Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T06:03:25.876Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:4</t>
+  </si>
+  <si>
+    <t>2026-06-06T05:58:10.824Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T06:03:23.647Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T06:06:59.337Z</t>
+  </si>
+  <si>
+    <t>69f4451102805d82768ac1d5:45:5</t>
+  </si>
+  <si>
+    <t>2026-06-06T06:03:27.035Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T06:06:57.520Z</t>
+  </si>
+  <si>
+    <t>attentionCheckId</t>
+  </si>
+  <si>
+    <t>attentionCheckKind</t>
+  </si>
+  <si>
+    <t>attentionCheckPrompt</t>
+  </si>
+  <si>
+    <t>attentionCheckAnswer</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:56:56.066Z</t>
+  </si>
+  <si>
+    <t>test_1__admin_1780934204236-xol2cht4:31:0</t>
+  </si>
+  <si>
+    <t>test_1__admin_1780934204236-xol2cht4</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:56:46.881Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:56:53.667Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:59:12.944Z</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780934341559-y5ctt1x2:25:0</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780934341559-y5ctt1x2</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:59:04.187Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:59:11.351Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:01:53.236Z</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780934341559-y5ctt1x2:25:1</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:59:14.964Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:01:49.218Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:02:25.033Z</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780934341559-y5ctt1x2:25:2</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:01:54.735Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:02:21.517Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:04:32.363Z</t>
+  </si>
+  <si>
+    <t>test_1__admin_1780934204236-xol2cht4:31:1</t>
+  </si>
+  <si>
+    <t>2026-06-08T15:56:56.924Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:04:30.087Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:07:49.624Z</t>
+  </si>
+  <si>
+    <t>test_1:1:5</t>
+  </si>
+  <si>
+    <t>test_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi hi hi </t>
+  </si>
+  <si>
+    <t>2026-05-28T02:33:39.777Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:07:47.054Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T21:10:06.644Z</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780952812466-80o338ph:1:0</t>
+  </si>
+  <si>
+    <t>test_2__admin_1780952812466-80o338ph</t>
+  </si>
+  <si>
+    <t>2026-06-08T21:08:09.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T21:10:04.225Z</t>
+  </si>
+  <si>
+    <t>2026-06-09T16:13:28.401Z</t>
+  </si>
+  <si>
+    <t>test2_admin__admin_1781021448638-fgtx3azr:6:0</t>
+  </si>
+  <si>
+    <t>test2_admin__admin_1781021448638-fgtx3azr</t>
+  </si>
+  <si>
+    <t>2026-06-09T16:10:50.581Z</t>
+  </si>
+  <si>
+    <t>2026-06-09T16:13:24.793Z</t>
+  </si>
+  <si>
     <t>questionnaireVersion</t>
   </si>
   <si>
@@ -5880,6 +6823,313 @@
   </si>
   <si>
     <t>My ideal mental rehearsal guidance would help me feel calm, focused, and prepared before the day starts. It would begin with a short grounding moment, then guide me to picture my main priorities, the challenges I may face, and how I want to handle them.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:27.415Z</t>
+  </si>
+  <si>
+    <t>6a1e0c3ca12895b8ceb08628:23:questionnaire</t>
+  </si>
+  <si>
+    <t>potential_obstacle_visualization,day_success_visualization,mind_grounding,body_grounding,task_success_visualization,value_grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:00:32.170Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:26.717Z</t>
+  </si>
+  <si>
+    <t>Laying out my tasks for the day. Ordering them in terms of priority. Allowing for disruptions and giving myself enough options.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:34.387Z</t>
+  </si>
+  <si>
+    <t>695fe101e718a910de31cbab:17:questionnaire</t>
+  </si>
+  <si>
+    <t>step_by_step,adaptive,moderate</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:58:02.046Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:32.774Z</t>
+  </si>
+  <si>
+    <t>Reflect on accomplishments, reflect on capabilities, review the day ahead, review the tasks, anticipate obstacles, relax the mind</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:06:02.186Z</t>
+  </si>
+  <si>
+    <t>60843a5bac9fbcc4a389cf29:8:questionnaire</t>
+  </si>
+  <si>
+    <t>0-12</t>
+  </si>
+  <si>
+    <t>mind_grounding,day_success_visualization,body_grounding,task_success_visualization,value_grounding,potential_obstacle_visualization</t>
+  </si>
+  <si>
+    <t>interactive_steps,readable_text</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:02:54.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:05:59.470Z</t>
+  </si>
+  <si>
+    <t>I would prefer meditating to gain calmness and increase my mental focus and application.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:07:00.561Z</t>
+  </si>
+  <si>
+    <t>6984afed1eac95dcf5fbe02d:25:questionnaire</t>
+  </si>
+  <si>
+    <t>day_success_visualization,task_success_visualization,value_grounding,mind_grounding,body_grounding,potential_obstacle_visualization</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:05:13.100Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:06:59.380Z</t>
+  </si>
+  <si>
+    <t>An audio speech with ambient music</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:08:17.601Z</t>
+  </si>
+  <si>
+    <t>6a00297ff9c814c9d89abd9d:30:questionnaire</t>
+  </si>
+  <si>
+    <t>value_grounding,day_success_visualization,task_success_visualization,potential_obstacle_visualization,body_grounding,mind_grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:30.378Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:07:19.427Z</t>
+  </si>
+  <si>
+    <t>Just something that tells me what to do regarding my schedule as well as a motivative sentence or phrase to get me through the day.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:35.775Z</t>
+  </si>
+  <si>
+    <t>67c045fa5074c5500ca40e76:42:questionnaire</t>
+  </si>
+  <si>
+    <t>1-15_plus</t>
+  </si>
+  <si>
+    <t>task_success_visualization,potential_obstacle_visualization,day_success_visualization,body_grounding,mind_grounding,value_grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:13:25.240Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:19:33.742Z</t>
+  </si>
+  <si>
+    <t>Relaxing my self and  Identify what I need to do in this day, start with difficult tasks when I get tired I do easy tasks for the day.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:25:37.793Z</t>
+  </si>
+  <si>
+    <t>69f99d99ddda26fa34296650:15:questionnaire</t>
+  </si>
+  <si>
+    <t>day_success_visualization,mind_grounding,potential_obstacle_visualization,task_success_visualization,value_grounding,body_grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:24:21.343Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:25:36.377Z</t>
+  </si>
+  <si>
+    <t>Listening to someone speaking aloud so I can do it while I complete tasks and visualise myself following it</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:26:31.328Z</t>
+  </si>
+  <si>
+    <t>6710fc99667069679076d2a2:42:questionnaire</t>
+  </si>
+  <si>
+    <t>first_person,second_person,third_person</t>
+  </si>
+  <si>
+    <t>adaptive,light,step_by_step,moderate</t>
+  </si>
+  <si>
+    <t>ambient,piano_lofi,energizing</t>
+  </si>
+  <si>
+    <t>calm_supportive,practical_direct,reflective,encouraging</t>
+  </si>
+  <si>
+    <t>mind_grounding,task_success_visualization,day_success_visualization,potential_obstacle_visualization,value_grounding,body_grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:32.815Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:26:27.882Z</t>
+  </si>
+  <si>
+    <t>I think a short and a steady script that can begin with a breath and body grounding</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:26:47.188Z</t>
+  </si>
+  <si>
+    <t>6a12b505a750756f1aa15320:2:questionnaire</t>
+  </si>
+  <si>
+    <t>first_person,third_person,second_person,no_preference</t>
+  </si>
+  <si>
+    <t>adaptive,step_by_step</t>
+  </si>
+  <si>
+    <t>interactive_steps,readable_text,spoken_audio</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:55.467Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:26:45.724Z</t>
+  </si>
+  <si>
+    <t>I often say that everything happens for the sake of good, so even if you think you made a bad decision, one good thing would probably come from it, and you'd be thankful that you chose this decision for that one thing.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:29:52.292Z</t>
+  </si>
+  <si>
+    <t>6a16e48625a8729b8578bbaa:12:questionnaire</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:22:01.785Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:29:52.737Z</t>
+  </si>
+  <si>
+    <t>My ideal mental rehearsal would help me start the day with clarity, purpose, and confidence. 
+It includes a brief review of my priorities, encouragement to stay focused on what I can control, reminders of my strengths, and motivation to approach challenges with a positive mindset.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:41:27.578Z</t>
+  </si>
+  <si>
+    <t>6a229a63b2044a3b6694cdf5:32:questionnaire</t>
+  </si>
+  <si>
+    <t>energizing</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:35:43.381Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:41:25.846Z</t>
+  </si>
+  <si>
+    <t>Adaptive in the level of support, background noise and length - long guides on low energy days might be hard to sit through; clear and encouraging, focusing more on being inspiring than overly detailed.</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:48.201Z</t>
+  </si>
+  <si>
+    <t>67eec9af24c42ed8971e8717:8:questionnaire</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:49:31.558Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:52:47.354Z</t>
+  </si>
+  <si>
+    <t>A calm place and I would let my body just get used to the routine, I think it would make everything ok</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:56:52.725Z</t>
+  </si>
+  <si>
+    <t>66718e6baa53bb3f83515a74:5:questionnaire</t>
+  </si>
+  <si>
+    <t>nature,energizing</t>
+  </si>
+  <si>
+    <t>practical_direct,encouraging,reflective</t>
+  </si>
+  <si>
+    <t>mind_grounding,value_grounding,day_success_visualization,task_success_visualization,body_grounding,potential_obstacle_visualization</t>
+  </si>
+  <si>
+    <t>text_and_audio,spoken_audio,readable_text</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:54:12.090Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:56:49.152Z</t>
+  </si>
+  <si>
+    <t>Reading and writing about my day and schedule</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:58:38.902Z</t>
+  </si>
+  <si>
+    <t>6a23107c00a1d8299a5cf0c4:18:questionnaire</t>
+  </si>
+  <si>
+    <t>none,nature,ambient</t>
+  </si>
+  <si>
+    <t>mind_grounding,body_grounding,day_success_visualization,value_grounding,task_success_visualization,potential_obstacle_visualization</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:56:35.441Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:58:39.147Z</t>
+  </si>
+  <si>
+    <t>Something that starts with body/mind presence meditation and then works into specific tasks for the day, ending with overarching goal/mantra reminder.</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:13:35.575Z</t>
+  </si>
+  <si>
+    <t>6a13cc1ae70f2f4c9036046c:32:questionnaire</t>
+  </si>
+  <si>
+    <t>day_success_visualization,task_success_visualization,mind_grounding,body_grounding,value_grounding,potential_obstacle_visualization</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:10:59.422Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T00:13:34.304Z</t>
+  </si>
+  <si>
+    <t>Everything is planned out entirely, step- by step to keep me on track. I feel encouraged and motivated to start the day that I have outlined ahead. Mentally and physically I am in a good position to move forward with my day.</t>
   </si>
 </sst>
 </file>
@@ -5942,6 +7192,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -22615,7 +23869,7 @@
         <v>1443</v>
       </c>
       <c r="P329" s="2">
-        <v>315305.0</v>
+        <v>1526530.0</v>
       </c>
       <c r="Q329" s="1" t="s">
         <v>655</v>
@@ -23615,7 +24869,7 @@
         <v>1526</v>
       </c>
       <c r="P349" s="2">
-        <v>358540.0</v>
+        <v>1212377.0</v>
       </c>
       <c r="Q349" s="1" t="s">
         <v>655</v>
@@ -24115,7 +25369,7 @@
         <v>1566</v>
       </c>
       <c r="P359" s="2">
-        <v>177965.0</v>
+        <v>855156.0</v>
       </c>
       <c r="Q359" s="1" t="s">
         <v>655</v>
@@ -24219,6 +25473,3256 @@
       </c>
       <c r="Q361" s="1" t="s">
         <v>1494</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E362" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F362" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G362" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H362" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J362" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K362" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L362" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N362" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="O362" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="P362" s="2">
+        <v>135801.0</v>
+      </c>
+      <c r="Q362" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E363" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="F363" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G363" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H363" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K363" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L363" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N363" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O363" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="P363" s="2">
+        <v>119698.0</v>
+      </c>
+      <c r="Q363" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E364" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F364" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G364" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H364" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K364" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L364" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N364" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="O364" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="P364" s="2">
+        <v>85800.0</v>
+      </c>
+      <c r="Q364" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E365" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F365" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G365" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H365" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J365" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K365" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L365" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N365" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="O365" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="P365" s="2">
+        <v>377920.0</v>
+      </c>
+      <c r="Q365" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E366" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F366" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G366" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H366" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J366" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K366" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L366" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N366" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="O366" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="P366" s="2">
+        <v>677286.0</v>
+      </c>
+      <c r="Q366" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E367" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F367" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G367" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H367" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J367" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K367" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L367" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="N367" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="O367" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="P367" s="2">
+        <v>183928.0</v>
+      </c>
+      <c r="Q367" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E368" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="F368" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H368" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K368" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L368" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N368" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="O368" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="P368" s="2">
+        <v>172751.0</v>
+      </c>
+      <c r="Q368" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E369" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F369" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J369" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K369" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L369" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N369" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="O369" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="P369" s="2">
+        <v>46583.0</v>
+      </c>
+      <c r="Q369" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E370" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F370" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G370" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H370" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J370" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K370" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L370" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N370" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="O370" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="P370" s="2">
+        <v>207059.0</v>
+      </c>
+      <c r="Q370" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E371" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F371" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H371" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K371" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L371" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N371" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="O371" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="P371" s="2">
+        <v>514010.0</v>
+      </c>
+      <c r="Q371" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E372" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F372" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G372" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H372" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K372" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L372" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N372" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="O372" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="P372" s="2">
+        <v>404354.0</v>
+      </c>
+      <c r="Q372" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E373" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F373" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G373" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H373" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K373" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L373" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N373" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="O373" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="P373" s="2">
+        <v>536440.0</v>
+      </c>
+      <c r="Q373" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E374" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F374" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G374" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J374" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K374" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L374" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N374" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="O374" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="P374" s="2">
+        <v>305992.0</v>
+      </c>
+      <c r="Q374" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E375" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F375" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G375" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H375" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K375" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L375" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N375" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="O375" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="P375" s="2">
+        <v>68064.0</v>
+      </c>
+      <c r="Q375" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E376" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F376" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G376" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H376" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J376" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K376" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L376" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N376" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="O376" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="P376" s="2">
+        <v>297277.0</v>
+      </c>
+      <c r="Q376" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E377" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F377" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G377" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H377" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J377" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K377" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L377" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N377" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="O377" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="P377" s="2">
+        <v>196586.0</v>
+      </c>
+      <c r="Q377" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E378" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F378" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G378" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H378" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K378" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L378" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N378" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="O378" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="P378" s="2">
+        <v>109960.0</v>
+      </c>
+      <c r="Q378" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E379" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F379" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G379" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H379" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J379" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K379" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L379" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N379" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="O379" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="P379" s="2">
+        <v>114920.0</v>
+      </c>
+      <c r="Q379" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E380" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F380" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G380" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H380" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K380" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="L380" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N380" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="O380" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="P380" s="2">
+        <v>465766.0</v>
+      </c>
+      <c r="Q380" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E381" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F381" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G381" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H381" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J381" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K381" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L381" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N381" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="O381" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="P381" s="2">
+        <v>78330.0</v>
+      </c>
+      <c r="Q381" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E382" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F382" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G382" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H382" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J382" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K382" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L382" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N382" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="O382" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="P382" s="2">
+        <v>56468.0</v>
+      </c>
+      <c r="Q382" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E383" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F383" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G383" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H383" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J383" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K383" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L383" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N383" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="O383" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P383" s="2">
+        <v>536271.0</v>
+      </c>
+      <c r="Q383" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E384" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F384" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G384" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H384" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J384" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K384" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L384" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N384" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="O384" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="P384" s="2">
+        <v>66446.0</v>
+      </c>
+      <c r="Q384" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E385" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F385" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G385" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H385" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J385" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K385" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L385" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N385" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="O385" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="P385" s="2">
+        <v>82153.0</v>
+      </c>
+      <c r="Q385" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E386" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F386" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G386" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H386" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J386" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K386" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L386" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N386" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="O386" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="P386" s="2">
+        <v>101138.0</v>
+      </c>
+      <c r="Q386" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E387" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F387" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G387" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H387" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K387" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L387" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N387" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="O387" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P387" s="2">
+        <v>53916.0</v>
+      </c>
+      <c r="Q387" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E388" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F388" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G388" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H388" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J388" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K388" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L388" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N388" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="O388" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="P388" s="2">
+        <v>262027.0</v>
+      </c>
+      <c r="Q388" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E389" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F389" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G389" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H389" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K389" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L389" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N389" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="O389" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="P389" s="2">
+        <v>249434.0</v>
+      </c>
+      <c r="Q389" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E390" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F390" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G390" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H390" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J390" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K390" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L390" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N390" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="O390" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="P390" s="2">
+        <v>59235.0</v>
+      </c>
+      <c r="Q390" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E391" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F391" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G391" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H391" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J391" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K391" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L391" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N391" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O391" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="P391" s="2">
+        <v>73569.0</v>
+      </c>
+      <c r="Q391" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E392" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F392" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G392" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H392" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J392" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K392" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L392" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N392" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O392" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="P392" s="2">
+        <v>66233.0</v>
+      </c>
+      <c r="Q392" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E393" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F393" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G393" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H393" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K393" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L393" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N393" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="O393" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="P393" s="2">
+        <v>125378.0</v>
+      </c>
+      <c r="Q393" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E394" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F394" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G394" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H394" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K394" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L394" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N394" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="O394" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="P394" s="2">
+        <v>45796.0</v>
+      </c>
+      <c r="Q394" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E395" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F395" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G395" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H395" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K395" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L395" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N395" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="O395" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="P395" s="2">
+        <v>487681.0</v>
+      </c>
+      <c r="Q395" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E396" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F396" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G396" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H396" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I396" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K396" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L396" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N396" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="O396" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="P396" s="2">
+        <v>503580.0</v>
+      </c>
+      <c r="Q396" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E397" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F397" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G397" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H397" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K397" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L397" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N397" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="O397" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="P397" s="2">
+        <v>275114.0</v>
+      </c>
+      <c r="Q397" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E398" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F398" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G398" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H398" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K398" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L398" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N398" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="O398" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="P398" s="2">
+        <v>332732.0</v>
+      </c>
+      <c r="Q398" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E399" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F399" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G399" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H399" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I399" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J399" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K399" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L399" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N399" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="O399" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="P399" s="2">
+        <v>176920.0</v>
+      </c>
+      <c r="Q399" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E400" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F400" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G400" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H400" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I400" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J400" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K400" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L400" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N400" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="O400" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="P400" s="2">
+        <v>212684.0</v>
+      </c>
+      <c r="Q400" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E401" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F401" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G401" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H401" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I401" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J401" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K401" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L401" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N401" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="O401" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="P401" s="2">
+        <v>127296.0</v>
+      </c>
+      <c r="Q401" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E402" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F402" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G402" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H402" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I402" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K402" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L402" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N402" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="O402" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="P402" s="2">
+        <v>57176.0</v>
+      </c>
+      <c r="Q402" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E403" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F403" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G403" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I403" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J403" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K403" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L403" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N403" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O403" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="P403" s="2">
+        <v>143887.0</v>
+      </c>
+      <c r="Q403" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E404" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F404" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G404" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H404" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K404" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L404" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N404" s="1" t="s">
+        <v>1752</v>
+      </c>
+      <c r="O404" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="P404" s="2">
+        <v>79783.0</v>
+      </c>
+      <c r="Q404" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E405" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F405" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G405" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H405" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I405" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K405" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L405" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N405" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="O405" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="P405" s="2">
+        <v>77005.0</v>
+      </c>
+      <c r="Q405" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E406" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F406" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G406" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H406" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I406" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J406" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K406" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L406" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N406" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="O406" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="P406" s="2">
+        <v>120058.0</v>
+      </c>
+      <c r="Q406" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E407" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F407" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G407" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H407" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I407" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J407" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K407" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L407" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N407" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="O407" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="P407" s="2">
+        <v>92955.0</v>
+      </c>
+      <c r="Q407" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E408" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F408" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G408" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H408" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I408" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J408" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K408" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L408" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N408" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="O408" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="P408" s="2">
+        <v>88829.0</v>
+      </c>
+      <c r="Q408" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E409" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F409" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G409" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H409" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I409" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J409" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K409" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L409" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N409" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="O409" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P409" s="2">
+        <v>106273.0</v>
+      </c>
+      <c r="Q409" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E410" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F410" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G410" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H410" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I410" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J410" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K410" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L410" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N410" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="O410" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="P410" s="2">
+        <v>242466.0</v>
+      </c>
+      <c r="Q410" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E411" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F411" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G411" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H411" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I411" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J411" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K411" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L411" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N411" s="1" t="s">
+        <v>1782</v>
+      </c>
+      <c r="O411" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="P411" s="2">
+        <v>88105.0</v>
+      </c>
+      <c r="Q411" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E412" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F412" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G412" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H412" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I412" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J412" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K412" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L412" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N412" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="O412" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="P412" s="2">
+        <v>88044.0</v>
+      </c>
+      <c r="Q412" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E413" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F413" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G413" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H413" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I413" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J413" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K413" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L413" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N413" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="O413" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="P413" s="2">
+        <v>86380.0</v>
+      </c>
+      <c r="Q413" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E414" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F414" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G414" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H414" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I414" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J414" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K414" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L414" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N414" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="O414" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="P414" s="2">
+        <v>168669.0</v>
+      </c>
+      <c r="Q414" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E415" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F415" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G415" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H415" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I415" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J415" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K415" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L415" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N415" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="O415" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="P415" s="2">
+        <v>69352.0</v>
+      </c>
+      <c r="Q415" s="1" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E416" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F416" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G416" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H416" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I416" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J416" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K416" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L416" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="N416" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="O416" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="P416" s="2">
+        <v>224691.0</v>
+      </c>
+      <c r="Q416" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E417" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F417" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G417" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H417" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I417" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J417" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K417" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L417" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N417" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="O417" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="P417" s="2">
+        <v>206772.0</v>
+      </c>
+      <c r="Q417" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E418" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F418" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G418" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H418" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I418" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J418" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K418" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="L418" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="N418" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="O418" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P418" s="2">
+        <v>95221.0</v>
+      </c>
+      <c r="Q418" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E419" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F419" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G419" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H419" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I419" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K419" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L419" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N419" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="O419" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="P419" s="2">
+        <v>232402.0</v>
+      </c>
+      <c r="Q419" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E420" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F420" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G420" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H420" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I420" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K420" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="L420" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N420" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="O420" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="P420" s="2">
+        <v>126303.0</v>
+      </c>
+      <c r="Q420" s="1" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E421" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F421" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G421" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H421" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I421" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J421" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K421" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L421" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N421" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="O421" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="P421" s="2">
+        <v>2.3147416E7</v>
+      </c>
+      <c r="Q421" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E422" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F422" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G422" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H422" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I422" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J422" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K422" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L422" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N422" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="O422" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="P422" s="2">
+        <v>164814.0</v>
+      </c>
+      <c r="Q422" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E423" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F423" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G423" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H423" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I423" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J423" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K423" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L423" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N423" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="O423" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="P423" s="2">
+        <v>264253.0</v>
+      </c>
+      <c r="Q423" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E424" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F424" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G424" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H424" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I424" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J424" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K424" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L424" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N424" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="O424" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="P424" s="2">
+        <v>295162.0</v>
+      </c>
+      <c r="Q424" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E425" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F425" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G425" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H425" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I425" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J425" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K425" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L425" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N425" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="O425" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="P425" s="2">
+        <v>312823.0</v>
+      </c>
+      <c r="Q425" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E426" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="F426" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G426" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H426" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I426" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J426" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K426" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="L426" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N426" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="O426" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="P426" s="2">
+        <v>210485.0</v>
+      </c>
+      <c r="Q426" s="1" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -24250,49 +28754,535 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1575</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1576</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1577</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1578</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1579</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1580</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1581</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1582</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1583</v>
+        <v>1847</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1584</v>
+        <v>1848</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1585</v>
+        <v>1849</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1586</v>
+        <v>1850</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1587</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1588</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1589</v>
+        <v>13</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E2" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="P2" s="2">
+        <v>6786.0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E3" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="P3" s="2">
+        <v>7164.0</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E4" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="P4" s="2">
+        <v>154254.0</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E5" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="P5" s="2">
+        <v>26782.0</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E6" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="P6" s="2">
+        <v>453164.0</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="V7" s="2">
+        <v>9.99247277E8</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="V8" s="2">
+        <v>115220.0</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="V9" s="2">
+        <v>154212.0</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>1903</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>13</v>
@@ -24307,18 +29297,18 @@
         <v>16</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1590</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>1591</v>
+        <v>1905</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1592</v>
+        <v>1906</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>22</v>
@@ -24327,34 +29317,34 @@
         <v>25.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1595</v>
+        <v>1909</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1596</v>
+        <v>1910</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>1598</v>
+        <v>1912</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>1599</v>
+        <v>1913</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>1600</v>
+        <v>1914</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>1601</v>
+        <v>1915</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>1602</v>
+        <v>1916</v>
       </c>
       <c r="W2" s="2">
         <v>69617.0</v>
@@ -24363,18 +29353,18 @@
         <v>29</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1603</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>1604</v>
+        <v>1918</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1605</v>
+        <v>1919</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>61</v>
@@ -24383,34 +29373,34 @@
         <v>13.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>1609</v>
+        <v>1923</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>1611</v>
+        <v>1925</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>1612</v>
+        <v>1926</v>
       </c>
       <c r="W3" s="2">
         <v>54271.0</v>
@@ -24419,18 +29409,18 @@
         <v>65</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>1613</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>1614</v>
+        <v>1928</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1615</v>
+        <v>1929</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>99</v>
@@ -24439,34 +29429,34 @@
         <v>43.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1616</v>
+        <v>1930</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1617</v>
+        <v>1931</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1619</v>
+        <v>1933</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1598</v>
+        <v>1912</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>1620</v>
+        <v>1934</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>1622</v>
+        <v>1936</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>1623</v>
+        <v>1937</v>
       </c>
       <c r="W4" s="2">
         <v>114534.0</v>
@@ -24475,18 +29465,18 @@
         <v>102</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>1624</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>1625</v>
+        <v>1939</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1626</v>
+        <v>1940</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>93</v>
@@ -24495,34 +29485,34 @@
         <v>32.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1627</v>
+        <v>1941</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1628</v>
+        <v>1942</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1629</v>
+        <v>1943</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1630</v>
+        <v>1944</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>1631</v>
+        <v>1945</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>1632</v>
+        <v>1946</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>1633</v>
+        <v>1947</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>1634</v>
+        <v>1948</v>
       </c>
       <c r="W5" s="2">
         <v>96760.0</v>
@@ -24531,18 +29521,18 @@
         <v>96</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>1635</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>1636</v>
+        <v>1950</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1637</v>
+        <v>1951</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>166</v>
@@ -24551,34 +29541,34 @@
         <v>3.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1595</v>
+        <v>1909</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1639</v>
+        <v>1953</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>1640</v>
+        <v>1954</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>1641</v>
+        <v>1955</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>1642</v>
+        <v>1956</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>1643</v>
+        <v>1957</v>
       </c>
       <c r="W6" s="2">
         <v>85219.0</v>
@@ -24587,18 +29577,18 @@
         <v>37</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>1644</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>1645</v>
+        <v>1959</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1646</v>
+        <v>1960</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>32</v>
@@ -24607,34 +29597,34 @@
         <v>15.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1647</v>
+        <v>1961</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M7" s="3">
         <v>46027.0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1649</v>
+        <v>1963</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>1650</v>
+        <v>1964</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>1651</v>
+        <v>1965</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>1652</v>
+        <v>1966</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>1653</v>
+        <v>1967</v>
       </c>
       <c r="W7" s="2">
         <v>260840.0</v>
@@ -24643,18 +29633,18 @@
         <v>37</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>1654</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>1655</v>
+        <v>1969</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1656</v>
+        <v>1970</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>219</v>
@@ -24663,34 +29653,34 @@
         <v>21.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1647</v>
+        <v>1961</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1657</v>
+        <v>1971</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1658</v>
+        <v>1972</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1598</v>
+        <v>1912</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>1659</v>
+        <v>1973</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>1660</v>
+        <v>1974</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>1661</v>
+        <v>1975</v>
       </c>
       <c r="W8" s="2">
         <v>92022.0</v>
@@ -24699,18 +29689,18 @@
         <v>222</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>1662</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>1663</v>
+        <v>1977</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1664</v>
+        <v>1978</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
@@ -24719,34 +29709,34 @@
         <v>47.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1627</v>
+        <v>1941</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1665</v>
+        <v>1979</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>1629</v>
+        <v>1943</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1666</v>
+        <v>1980</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>1667</v>
+        <v>1981</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>1668</v>
+        <v>1982</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>1669</v>
+        <v>1983</v>
       </c>
       <c r="W9" s="2">
         <v>221157.0</v>
@@ -24755,18 +29745,18 @@
         <v>58</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>1670</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>1671</v>
+        <v>1985</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1672</v>
+        <v>1986</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
@@ -24775,34 +29765,34 @@
         <v>8.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>1674</v>
+        <v>1988</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>1641</v>
+        <v>1955</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>1675</v>
+        <v>1989</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>1676</v>
+        <v>1990</v>
       </c>
       <c r="W10" s="2">
         <v>120158.0</v>
@@ -24811,18 +29801,18 @@
         <v>51</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>1677</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>1678</v>
+        <v>1992</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1679</v>
+        <v>1993</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>281</v>
@@ -24831,34 +29821,34 @@
         <v>3.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>1680</v>
+        <v>1994</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>1681</v>
+        <v>1995</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>1682</v>
+        <v>1996</v>
       </c>
       <c r="W11" s="2">
         <v>185151.0</v>
@@ -24867,18 +29857,18 @@
         <v>284</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>1683</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>1684</v>
+        <v>1998</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1685</v>
+        <v>1999</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>124</v>
@@ -24887,34 +29877,34 @@
         <v>35.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>1639</v>
+        <v>1953</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1687</v>
+        <v>2001</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>1688</v>
+        <v>2002</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>1689</v>
+        <v>2003</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>1690</v>
+        <v>2004</v>
       </c>
       <c r="W12" s="2">
         <v>169824.0</v>
@@ -24923,18 +29913,18 @@
         <v>121</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>1691</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1692</v>
+        <v>2006</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1693</v>
+        <v>2007</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>208</v>
@@ -24943,34 +29933,34 @@
         <v>19.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M13" s="3">
         <v>46086.0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>1694</v>
+        <v>2008</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>1695</v>
+        <v>2009</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>1696</v>
+        <v>2010</v>
       </c>
       <c r="W13" s="2">
         <v>184911.0</v>
@@ -24979,18 +29969,18 @@
         <v>65</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>1697</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>1698</v>
+        <v>2012</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1699</v>
+        <v>2013</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>225</v>
@@ -24999,34 +29989,34 @@
         <v>35.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>1700</v>
+        <v>2014</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>1701</v>
+        <v>2015</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>1702</v>
+        <v>2016</v>
       </c>
       <c r="W14" s="2">
         <v>132948.0</v>
@@ -25035,18 +30025,18 @@
         <v>228</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>1703</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>1704</v>
+        <v>2018</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1705</v>
+        <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>183</v>
@@ -25055,34 +30045,34 @@
         <v>24.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M15" s="3">
         <v>46027.0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>1706</v>
+        <v>2020</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>1707</v>
+        <v>2021</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>1708</v>
+        <v>2022</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>1709</v>
+        <v>2023</v>
       </c>
       <c r="W15" s="2">
         <v>206686.0</v>
@@ -25091,18 +30081,18 @@
         <v>37</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>1710</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>1711</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1712</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>148</v>
@@ -25111,34 +30101,34 @@
         <v>25.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1647</v>
+        <v>1961</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>1713</v>
+        <v>2027</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>1714</v>
+        <v>2028</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>1715</v>
+        <v>2029</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>1716</v>
+        <v>2030</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>1717</v>
+        <v>2031</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>1718</v>
+        <v>2032</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>1719</v>
+        <v>2033</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>1720</v>
+        <v>2034</v>
       </c>
       <c r="W16" s="2">
         <v>191384.0</v>
@@ -25147,18 +30137,18 @@
         <v>102</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>1721</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1722</v>
+        <v>2036</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1723</v>
+        <v>2037</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>157</v>
@@ -25167,34 +30157,34 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>1595</v>
+        <v>1909</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1619</v>
+        <v>1933</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>1724</v>
+        <v>2038</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>1725</v>
+        <v>2039</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>1726</v>
+        <v>2040</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>1727</v>
+        <v>2041</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>1728</v>
+        <v>2042</v>
       </c>
       <c r="W17" s="2">
         <v>199605.0</v>
@@ -25203,18 +30193,18 @@
         <v>121</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>1729</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>1730</v>
+        <v>2044</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1731</v>
+        <v>2045</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>231</v>
@@ -25223,34 +30213,34 @@
         <v>26.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M18" s="3">
         <v>46089.0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1733</v>
+        <v>2047</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>1700</v>
+        <v>2014</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>1707</v>
+        <v>2021</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>1734</v>
+        <v>2048</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>1735</v>
+        <v>2049</v>
       </c>
       <c r="W18" s="2">
         <v>127713.0</v>
@@ -25259,18 +30249,18 @@
         <v>37</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>1736</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>1737</v>
+        <v>2051</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1738</v>
+        <v>2052</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>113</v>
@@ -25279,34 +30269,34 @@
         <v>42.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1739</v>
+        <v>2053</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>1740</v>
+        <v>2054</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1596</v>
+        <v>1910</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1741</v>
+        <v>2055</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1630</v>
+        <v>1944</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>1742</v>
+        <v>2056</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>1600</v>
+        <v>1914</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>1743</v>
+        <v>2057</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>1744</v>
+        <v>2058</v>
       </c>
       <c r="W19" s="2">
         <v>242549.0</v>
@@ -25315,18 +30305,18 @@
         <v>102</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>1745</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1746</v>
+        <v>2060</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1747</v>
+        <v>2061</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>252</v>
@@ -25335,34 +30325,34 @@
         <v>33.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1748</v>
+        <v>2062</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>1749</v>
+        <v>2063</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>1750</v>
+        <v>2064</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>1630</v>
+        <v>1944</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>1751</v>
+        <v>2065</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>1752</v>
+        <v>2066</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>1753</v>
+        <v>2067</v>
       </c>
       <c r="W20" s="2">
         <v>154472.0</v>
@@ -25371,18 +30361,18 @@
         <v>37</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>1754</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>1755</v>
+        <v>2069</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1756</v>
+        <v>2070</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>456</v>
@@ -25391,34 +30381,34 @@
         <v>14.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>1757</v>
+        <v>2071</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>1758</v>
+        <v>2072</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>1759</v>
+        <v>2073</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>1760</v>
+        <v>2074</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>1761</v>
+        <v>2075</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>1762</v>
+        <v>2076</v>
       </c>
       <c r="W21" s="2">
         <v>165984.0</v>
@@ -25427,18 +30417,18 @@
         <v>459</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>1763</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>1764</v>
+        <v>2078</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1765</v>
+        <v>2079</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>334</v>
@@ -25447,34 +30437,34 @@
         <v>8.0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1616</v>
+        <v>1930</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>1766</v>
+        <v>2080</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>1767</v>
+        <v>2081</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>1768</v>
+        <v>2082</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>1769</v>
+        <v>2083</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>1770</v>
+        <v>2084</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>1771</v>
+        <v>2085</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>1772</v>
+        <v>2086</v>
       </c>
       <c r="W22" s="2">
         <v>354873.0</v>
@@ -25483,18 +30473,18 @@
         <v>65</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>1773</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>1774</v>
+        <v>2088</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1775</v>
+        <v>2089</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>402</v>
@@ -25503,34 +30493,34 @@
         <v>18.0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M23" s="3">
         <v>46027.0</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1768</v>
+        <v>2082</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>1776</v>
+        <v>2090</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>1777</v>
+        <v>2091</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>1778</v>
+        <v>2092</v>
       </c>
       <c r="W23" s="2">
         <v>124934.0</v>
@@ -25539,18 +30529,18 @@
         <v>405</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>1779</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>1780</v>
+        <v>2094</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1781</v>
+        <v>2095</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>194</v>
@@ -25559,34 +30549,34 @@
         <v>0.0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1647</v>
+        <v>1961</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>1782</v>
+        <v>2096</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1628</v>
+        <v>1942</v>
       </c>
       <c r="M24" s="3">
         <v>46086.0</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1783</v>
+        <v>2097</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>1784</v>
+        <v>2098</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>1785</v>
+        <v>2099</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>1786</v>
+        <v>2100</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>1787</v>
+        <v>2101</v>
       </c>
       <c r="W24" s="2">
         <v>350739.0</v>
@@ -25595,18 +30585,18 @@
         <v>197</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>1788</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>1789</v>
+        <v>2103</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1790</v>
+        <v>2104</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>328</v>
@@ -25615,34 +30605,34 @@
         <v>1.0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>1619</v>
+        <v>1933</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>1791</v>
+        <v>2105</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>1792</v>
+        <v>2106</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>1793</v>
+        <v>2107</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>1794</v>
+        <v>2108</v>
       </c>
       <c r="W25" s="2">
         <v>215622.0</v>
@@ -25651,18 +30641,18 @@
         <v>331</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>1795</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>1796</v>
+        <v>2110</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1797</v>
+        <v>2111</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>213</v>
@@ -25671,34 +30661,34 @@
         <v>6.0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>1639</v>
+        <v>1953</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>1640</v>
+        <v>1954</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>1798</v>
+        <v>2112</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>1799</v>
+        <v>2113</v>
       </c>
       <c r="W26" s="2">
         <v>108912.0</v>
@@ -25707,18 +30697,18 @@
         <v>216</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>1800</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>1801</v>
+        <v>2115</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1802</v>
+        <v>2116</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>134</v>
@@ -25727,34 +30717,34 @@
         <v>39.0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1748</v>
+        <v>2062</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M27" s="3">
         <v>46058.0</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>1803</v>
+        <v>2117</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>1707</v>
+        <v>2021</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>1804</v>
+        <v>2118</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>1805</v>
+        <v>2119</v>
       </c>
       <c r="W27" s="2">
         <v>326389.0</v>
@@ -25763,18 +30753,18 @@
         <v>137</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>1806</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>1807</v>
+        <v>2121</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1808</v>
+        <v>2122</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>437</v>
@@ -25783,34 +30773,34 @@
         <v>16.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>1741</v>
+        <v>2055</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>1809</v>
+        <v>2123</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>1810</v>
+        <v>2124</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>1811</v>
+        <v>2125</v>
       </c>
       <c r="W28" s="2">
         <v>117154.0</v>
@@ -25819,18 +30809,18 @@
         <v>37</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>1812</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>1813</v>
+        <v>2127</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1814</v>
+        <v>2128</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>670</v>
@@ -25839,34 +30829,34 @@
         <v>3.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M29" s="3">
         <v>46086.0</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>1815</v>
+        <v>2129</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>1816</v>
+        <v>2130</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>1817</v>
+        <v>2131</v>
       </c>
       <c r="W29" s="2">
         <v>89443.0</v>
@@ -25875,18 +30865,18 @@
         <v>378</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>1818</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>1819</v>
+        <v>2133</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1820</v>
+        <v>2134</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>640</v>
@@ -25895,34 +30885,34 @@
         <v>6.0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>1750</v>
+        <v>2064</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>1821</v>
+        <v>2135</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>1822</v>
+        <v>2136</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>1823</v>
+        <v>2137</v>
       </c>
       <c r="W30" s="2">
         <v>198693.0</v>
@@ -25931,18 +30921,18 @@
         <v>643</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>1824</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>1825</v>
+        <v>2139</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1826</v>
+        <v>2140</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>462</v>
@@ -25951,34 +30941,34 @@
         <v>35.0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>1639</v>
+        <v>1953</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>1827</v>
+        <v>2141</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>1828</v>
+        <v>2142</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>1829</v>
+        <v>2143</v>
       </c>
       <c r="W31" s="2">
         <v>313918.0</v>
@@ -25987,18 +30977,18 @@
         <v>102</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>1830</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>1831</v>
+        <v>2145</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1832</v>
+        <v>2146</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>789</v>
@@ -26007,34 +30997,34 @@
         <v>12.0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>1833</v>
+        <v>2147</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>1750</v>
+        <v>2064</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1834</v>
+        <v>2148</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>1742</v>
+        <v>2056</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>1835</v>
+        <v>2149</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>1836</v>
+        <v>2150</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>1837</v>
+        <v>2151</v>
       </c>
       <c r="W32" s="2">
         <v>94322.0</v>
@@ -26043,18 +31033,18 @@
         <v>102</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>1838</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>1839</v>
+        <v>2153</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1840</v>
+        <v>2154</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>188</v>
@@ -26063,34 +31053,34 @@
         <v>18.0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>1841</v>
+        <v>2155</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>1842</v>
+        <v>2156</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>1843</v>
+        <v>2157</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>1844</v>
+        <v>2158</v>
       </c>
       <c r="W33" s="2">
         <v>187252.0</v>
@@ -26099,18 +31089,18 @@
         <v>191</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>1845</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>1846</v>
+        <v>2160</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1847</v>
+        <v>2161</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>871</v>
@@ -26119,34 +31109,34 @@
         <v>23.0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1848</v>
+        <v>2162</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>1617</v>
+        <v>1931</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>1849</v>
+        <v>2163</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>1741</v>
+        <v>2055</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>1850</v>
+        <v>2164</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>1770</v>
+        <v>2084</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>1851</v>
+        <v>2165</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>1852</v>
+        <v>2166</v>
       </c>
       <c r="W34" s="2">
         <v>159803.0</v>
@@ -26155,18 +31145,18 @@
         <v>37</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>1853</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>1854</v>
+        <v>2168</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1855</v>
+        <v>2169</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>646</v>
@@ -26175,34 +31165,34 @@
         <v>40.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>1841</v>
+        <v>2155</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>1856</v>
+        <v>2170</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>1857</v>
+        <v>2171</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>1858</v>
+        <v>2172</v>
       </c>
       <c r="W35" s="2">
         <v>218999.0</v>
@@ -26211,18 +31201,18 @@
         <v>649</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>1859</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>1860</v>
+        <v>2174</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1861</v>
+        <v>2175</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>291</v>
@@ -26231,34 +31221,34 @@
         <v>30.0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>1849</v>
+        <v>2163</v>
       </c>
       <c r="M36" s="3">
         <v>46087.0</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>1687</v>
+        <v>2001</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>1862</v>
+        <v>2176</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>1726</v>
+        <v>2040</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>1863</v>
+        <v>2177</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>1864</v>
+        <v>2178</v>
       </c>
       <c r="W36" s="2">
         <v>297123.0</v>
@@ -26267,18 +31257,18 @@
         <v>37</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>1865</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>1866</v>
+        <v>2180</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1867</v>
+        <v>2181</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>479</v>
@@ -26287,34 +31277,34 @@
         <v>29.0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>1849</v>
+        <v>2163</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>1750</v>
+        <v>2064</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>1868</v>
+        <v>2182</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>1785</v>
+        <v>2099</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>1869</v>
+        <v>2183</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>1870</v>
+        <v>2184</v>
       </c>
       <c r="W37" s="2">
         <v>162054.0</v>
@@ -26323,18 +31313,18 @@
         <v>37</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>1871</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>1872</v>
+        <v>2186</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1873</v>
+        <v>2187</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>609</v>
@@ -26343,34 +31333,34 @@
         <v>44.0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>1657</v>
+        <v>1971</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>1767</v>
+        <v>2081</v>
       </c>
       <c r="M38" s="3">
         <v>46147.0</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>1666</v>
+        <v>1980</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>1815</v>
+        <v>2129</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>1874</v>
+        <v>2188</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>1875</v>
+        <v>2189</v>
       </c>
       <c r="W38" s="2">
         <v>135437.0</v>
@@ -26379,18 +31369,18 @@
         <v>191</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>1876</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>1877</v>
+        <v>2191</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1878</v>
+        <v>2192</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>442</v>
@@ -26399,34 +31389,34 @@
         <v>19.0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M39" s="3">
         <v>46152.0</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1687</v>
+        <v>2001</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>1879</v>
+        <v>2193</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>1880</v>
+        <v>2194</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>1881</v>
+        <v>2195</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>1882</v>
+        <v>2196</v>
       </c>
       <c r="W39" s="2">
         <v>516664.0</v>
@@ -26435,18 +31425,18 @@
         <v>445</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>1883</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>1884</v>
+        <v>2198</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1885</v>
+        <v>2199</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>568</v>
@@ -26455,34 +31445,34 @@
         <v>6.0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>1732</v>
+        <v>2046</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M40" s="3">
         <v>46309.0</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>1631</v>
+        <v>1945</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>1707</v>
+        <v>2021</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>1886</v>
+        <v>2200</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>1887</v>
+        <v>2201</v>
       </c>
       <c r="W40" s="2">
         <v>289116.0</v>
@@ -26491,18 +31481,18 @@
         <v>58</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>1888</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>1889</v>
+        <v>2203</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1890</v>
+        <v>2204</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>1079</v>
@@ -26511,34 +31501,34 @@
         <v>3.0</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>1757</v>
+        <v>2071</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>1891</v>
+        <v>2205</v>
       </c>
       <c r="M41" s="3">
         <v>46089.0</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>1768</v>
+        <v>2082</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>1892</v>
+        <v>2206</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>1893</v>
+        <v>2207</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>1894</v>
+        <v>2208</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>1895</v>
+        <v>2209</v>
       </c>
       <c r="W41" s="2">
         <v>144376.0</v>
@@ -26547,18 +31537,18 @@
         <v>37</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>1896</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>1897</v>
+        <v>2211</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1898</v>
+        <v>2212</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>1231</v>
@@ -26567,34 +31557,34 @@
         <v>19.0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M42" s="3">
         <v>46149.0</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1687</v>
+        <v>2001</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>1899</v>
+        <v>2213</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>1610</v>
+        <v>1924</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>1900</v>
+        <v>2214</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>1901</v>
+        <v>2215</v>
       </c>
       <c r="W42" s="2">
         <v>107906.0</v>
@@ -26603,18 +31593,18 @@
         <v>37</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>1902</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>1903</v>
+        <v>2217</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1904</v>
+        <v>2218</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>397</v>
@@ -26623,34 +31613,34 @@
         <v>9.0</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>1619</v>
+        <v>1933</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>1725</v>
+        <v>2039</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>1905</v>
+        <v>2219</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>1906</v>
+        <v>2220</v>
       </c>
       <c r="W43" s="2">
         <v>305099.0</v>
@@ -26659,18 +31649,18 @@
         <v>37</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>1907</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>1908</v>
+        <v>2222</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1909</v>
+        <v>2223</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1100</v>
@@ -26679,34 +31669,34 @@
         <v>15.0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>1686</v>
+        <v>2000</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>1910</v>
+        <v>2224</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>1911</v>
+        <v>2225</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>1880</v>
+        <v>2194</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>1912</v>
+        <v>2226</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>1913</v>
+        <v>2227</v>
       </c>
       <c r="W44" s="2">
         <v>171922.0</v>
@@ -26715,18 +31705,18 @@
         <v>1103</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>1914</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>1915</v>
+        <v>2229</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1916</v>
+        <v>2230</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>892</v>
@@ -26735,34 +31725,34 @@
         <v>21.0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1673</v>
+        <v>1987</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>1917</v>
+        <v>2231</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>1707</v>
+        <v>2021</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>1918</v>
+        <v>2232</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>1919</v>
+        <v>2233</v>
       </c>
       <c r="W45" s="2">
         <v>336823.0</v>
@@ -26771,18 +31761,18 @@
         <v>37</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>1920</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>1921</v>
+        <v>2235</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1922</v>
+        <v>2236</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1288</v>
@@ -26791,34 +31781,34 @@
         <v>46.0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>1923</v>
+        <v>2237</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>1597</v>
+        <v>1911</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>1924</v>
+        <v>2238</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>1925</v>
+        <v>2239</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>1926</v>
+        <v>2240</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>1927</v>
+        <v>2241</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>1928</v>
+        <v>2242</v>
       </c>
       <c r="W46" s="2">
         <v>98260.0</v>
@@ -26827,18 +31817,18 @@
         <v>37</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>1929</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>1930</v>
+        <v>2244</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1931</v>
+        <v>2245</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1309</v>
@@ -26847,34 +31837,34 @@
         <v>19.0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>1618</v>
+        <v>1932</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>1629</v>
+        <v>1943</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>1932</v>
+        <v>2246</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>1933</v>
+        <v>2247</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>1934</v>
+        <v>2248</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>1935</v>
+        <v>2249</v>
       </c>
       <c r="W47" s="2">
         <v>165672.0</v>
@@ -26883,18 +31873,18 @@
         <v>102</v>
       </c>
       <c r="Y47" s="1" t="s">
-        <v>1936</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>1937</v>
+        <v>2251</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1938</v>
+        <v>2252</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1377</v>
@@ -26903,34 +31893,34 @@
         <v>38.0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>1606</v>
+        <v>1920</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>1714</v>
+        <v>2028</v>
       </c>
       <c r="M48" s="3">
         <v>46027.0</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>1939</v>
+        <v>2253</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>1940</v>
+        <v>2254</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>1621</v>
+        <v>1935</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>1941</v>
+        <v>2255</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>1942</v>
+        <v>2256</v>
       </c>
       <c r="W48" s="2">
         <v>92133.0</v>
@@ -26939,18 +31929,18 @@
         <v>65</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>1943</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>1944</v>
+        <v>2258</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1945</v>
+        <v>2259</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1357</v>
@@ -26959,34 +31949,34 @@
         <v>41.0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1594</v>
+        <v>1908</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>1657</v>
+        <v>1971</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>1946</v>
+        <v>2260</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>1715</v>
+        <v>2029</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>1834</v>
+        <v>2148</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>1947</v>
+        <v>2261</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>1770</v>
+        <v>2084</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>1948</v>
+        <v>2262</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>1949</v>
+        <v>2263</v>
       </c>
       <c r="W49" s="2">
         <v>145004.0</v>
@@ -26995,18 +31985,18 @@
         <v>1360</v>
       </c>
       <c r="Y49" s="1" t="s">
-        <v>1950</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>1951</v>
+        <v>2265</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1952</v>
+        <v>2266</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1398</v>
@@ -27015,34 +32005,34 @@
         <v>47.0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1593</v>
+        <v>1907</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1638</v>
+        <v>1952</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>1648</v>
+        <v>1962</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>1607</v>
+        <v>1921</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>1639</v>
+        <v>1953</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1608</v>
+        <v>1922</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>1751</v>
+        <v>2065</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>1933</v>
+        <v>2247</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>1953</v>
+        <v>2267</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>1954</v>
+        <v>2268</v>
       </c>
       <c r="W50" s="2">
         <v>110650.0</v>
@@ -27051,7 +32041,847 @@
         <v>649</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>1955</v>
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E51" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="M51" s="3">
+        <v>46061.0</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="W51" s="2">
+        <v>114547.0</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E52" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="M52" s="3">
+        <v>46025.0</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="S52" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="W52" s="2">
+        <v>270729.0</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y52" s="1" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E53" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="W53" s="2">
+        <v>185343.0</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y53" s="1" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E54" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="W54" s="2">
+        <v>106280.0</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="Y54" s="1" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E55" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="W55" s="2">
+        <v>229049.0</v>
+      </c>
+      <c r="X55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y55" s="1" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E56" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>2304</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="W56" s="2">
+        <v>368503.0</v>
+      </c>
+      <c r="X56" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E57" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="W57" s="2">
+        <v>75034.0</v>
+      </c>
+      <c r="X57" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="Y57" s="1" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E58" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="W58" s="2">
+        <v>235067.0</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="Y58" s="1" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="W59" s="2">
+        <v>170257.0</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E60" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>2335</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="W60" s="2">
+        <v>470952.0</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y60" s="1" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E61" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="M61" s="3">
+        <v>46027.0</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="W61" s="2">
+        <v>342466.0</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y61" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E62" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>2170</v>
+      </c>
+      <c r="S62" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>2347</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="W62" s="2">
+        <v>195799.0</v>
+      </c>
+      <c r="X62" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y62" s="1" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="W63" s="2">
+        <v>157063.0</v>
+      </c>
+      <c r="X63" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y63" s="1" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E64" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="M64" s="3">
+        <v>46086.0</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="W64" s="2">
+        <v>123706.0</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="Y64" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E65" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="W65" s="2">
+        <v>154882.0</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>2371</v>
       </c>
     </row>
   </sheetData>
